--- a/Pruebas calificadas/COLEGIO GONZALO ARANGO (IED)_502_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO GONZALO ARANGO (IED)_502_CALIFICADO.xlsx
@@ -807,11 +807,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>111001104388</t>
@@ -1060,11 +1056,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>111001104388</t>
@@ -1313,11 +1305,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>111001104388</t>
@@ -1566,11 +1554,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>111001104388</t>
@@ -1819,11 +1803,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>111001104388</t>
@@ -2064,11 +2044,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>111001104388</t>
@@ -2309,11 +2285,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>111001104388</t>
@@ -2562,11 +2534,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>111001104388</t>
@@ -2815,11 +2783,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>111001104388</t>
@@ -3068,11 +3032,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>111001104388</t>
@@ -3309,11 +3269,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>111001104388</t>
@@ -3562,11 +3518,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t>111001104388</t>
@@ -3815,11 +3767,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="2" t="inlineStr">
         <is>
           <t>111001104388</t>
@@ -4068,11 +4016,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t>111001104388</t>
@@ -4321,11 +4265,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="inlineStr"/>
       <c r="B16" s="2" t="inlineStr">
         <is>
           <t>111001104388</t>
@@ -4574,11 +4514,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
           <t>111001104388</t>
@@ -4827,11 +4763,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="2" t="inlineStr">
         <is>
           <t>111001104388</t>
@@ -5080,11 +5012,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="inlineStr"/>
       <c r="B19" s="2" t="inlineStr">
         <is>
           <t>111001104388</t>
@@ -5333,11 +5261,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
           <t>111001104388</t>
@@ -5586,11 +5510,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
           <t>111001104388</t>
@@ -5839,11 +5759,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
           <t>111001104388</t>
@@ -6092,11 +6008,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
           <t>111001104388</t>
@@ -6345,11 +6257,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
           <t>111001104388</t>
@@ -6594,11 +6502,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
           <t>111001104388</t>
@@ -6839,11 +6743,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
           <t>111001104388</t>
@@ -7092,11 +6992,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
           <t>111001104388</t>
@@ -7345,11 +7241,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
           <t>111001104388</t>
@@ -7598,11 +7490,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
           <t>111001104388</t>
@@ -7851,11 +7739,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A30" s="2" t="inlineStr"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
           <t>111001104388</t>
@@ -8104,11 +7988,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
           <t>111001104388</t>
@@ -8357,11 +8237,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
           <t>111001104388</t>
@@ -8610,11 +8486,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="inlineStr"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
           <t>111001104388</t>
@@ -8859,11 +8731,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="inlineStr"/>
       <c r="B34" s="2" t="inlineStr">
         <is>
           <t>111001104388</t>
@@ -9112,11 +8980,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="inlineStr"/>
       <c r="B35" s="2" t="inlineStr">
         <is>
           <t>111001104388</t>
@@ -9365,11 +9229,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
           <t>111001104388</t>
@@ -9618,11 +9478,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A37" s="2" t="inlineStr"/>
       <c r="B37" s="2" t="inlineStr">
         <is>
           <t>111001104388</t>
@@ -9871,11 +9727,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="inlineStr"/>
       <c r="B38" s="2" t="inlineStr">
         <is>
           <t>111001104388</t>
@@ -10124,11 +9976,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
           <t>111001104388</t>
@@ -10373,11 +10221,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A40" s="2" t="inlineStr"/>
       <c r="B40" s="2" t="inlineStr">
         <is>
           <t>111001104388</t>
@@ -10626,11 +10470,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="inlineStr"/>
       <c r="B41" s="2" t="inlineStr">
         <is>
           <t>111001104388</t>
@@ -10879,11 +10719,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A42" s="2" t="inlineStr"/>
       <c r="B42" s="2" t="inlineStr">
         <is>
           <t>111001104388</t>
@@ -11132,11 +10968,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A43" s="2" t="inlineStr"/>
       <c r="B43" s="2" t="inlineStr">
         <is>
           <t>111001104388</t>
@@ -11373,11 +11205,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A44" s="2" t="inlineStr"/>
       <c r="B44" s="2" t="inlineStr">
         <is>
           <t>111001104388</t>
@@ -11626,11 +11454,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A45" s="2" t="inlineStr"/>
       <c r="B45" s="2" t="inlineStr">
         <is>
           <t>111001104388</t>
@@ -11879,11 +11703,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A46" s="2" t="inlineStr"/>
       <c r="B46" s="2" t="inlineStr">
         <is>
           <t>111001104388</t>
@@ -12132,11 +11952,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A47" s="2" t="inlineStr"/>
       <c r="B47" s="2" t="inlineStr">
         <is>
           <t>111001104388</t>
@@ -12385,11 +12201,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A48" s="2" t="inlineStr"/>
       <c r="B48" s="2" t="inlineStr">
         <is>
           <t>111001104388</t>
@@ -12638,11 +12450,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A49" s="2" t="inlineStr"/>
       <c r="B49" s="2" t="inlineStr">
         <is>
           <t>111001104388</t>
@@ -12891,11 +12699,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A50" s="2" t="inlineStr"/>
       <c r="B50" s="2" t="inlineStr">
         <is>
           <t>111001104388</t>
@@ -13144,11 +12948,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A51" s="2" t="inlineStr"/>
       <c r="B51" s="2" t="inlineStr">
         <is>
           <t>111001104388</t>
@@ -13397,11 +13197,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A52" s="2" t="inlineStr"/>
       <c r="B52" s="2" t="inlineStr">
         <is>
           <t>111001104388</t>
@@ -13650,11 +13446,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A53" s="2" t="inlineStr"/>
       <c r="B53" s="2" t="inlineStr">
         <is>
           <t>111001104388</t>
@@ -13903,11 +13695,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A54" s="2" t="inlineStr"/>
       <c r="B54" s="2" t="inlineStr">
         <is>
           <t>111001104388</t>
@@ -14156,11 +13944,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A55" s="2" t="inlineStr"/>
       <c r="B55" s="2" t="inlineStr">
         <is>
           <t>111001104388</t>
@@ -14409,11 +14193,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A56" s="2" t="inlineStr"/>
       <c r="B56" s="2" t="inlineStr">
         <is>
           <t>111001104388</t>
@@ -14662,11 +14442,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A57" s="2" t="inlineStr"/>
       <c r="B57" s="2" t="inlineStr">
         <is>
           <t>111001104388</t>
@@ -14915,11 +14691,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A58" s="2" t="inlineStr"/>
       <c r="B58" s="2" t="inlineStr">
         <is>
           <t>111001104388</t>
@@ -15168,11 +14940,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A59" s="2" t="inlineStr"/>
       <c r="B59" s="2" t="inlineStr">
         <is>
           <t>111001104388</t>
@@ -15421,11 +15189,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A60" s="2" t="inlineStr"/>
       <c r="B60" s="2" t="inlineStr">
         <is>
           <t>111001104388</t>
@@ -15674,11 +15438,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A61" s="2" t="inlineStr"/>
       <c r="B61" s="2" t="inlineStr">
         <is>
           <t>111001104388</t>
